--- a/MotiscanV2026-neuroprems/task_materials/text/appariementR2E2.xlsx
+++ b/MotiscanV2026-neuroprems/task_materials/text/appariementR2E2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adriana.papasavvas\Documents\GitHub\MotiscanV2024\task_materials\text\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://instituteicm-my.sharepoint.com/personal/adriana_papasavvas_icm-institute_org/Documents/Desktop/Neuroprems2026-modified/Neuroprems2026-main/MotiscanV2026-neuroprems/task_materials/text/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F883450-49D1-4102-97FC-D26928FE26C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{6F883450-49D1-4102-97FC-D26928FE26C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FE026ED-60BD-430D-AA63-1D3D90491197}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="14190" windowHeight="9900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="420" windowWidth="24495" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -348,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -401,7 +401,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -412,7 +412,7 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -420,7 +420,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -428,7 +428,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -444,7 +444,7 @@
         <v>5</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -489,7 +489,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>21</v>
@@ -497,58 +497,26 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>8</v>
-      </c>
-      <c r="B22">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>4</v>
-      </c>
-      <c r="B23">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>12</v>
-      </c>
-      <c r="B24">
         <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
